--- a/Book2_with_develle.xlsx
+++ b/Book2_with_develle.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DM101"/>
+  <dimension ref="A1:DO101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1010,12 +1010,22 @@
       </c>
       <c r="DL1" s="1" t="inlineStr">
         <is>
+          <t>mcharo_develle_ln_price</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
           <t>Whole_Number_Used</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>Prime_Factorization</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>mcharo_develle_price_eur</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1446,18 @@
         <v>3.261768853</v>
       </c>
       <c r="DL2" t="n">
+        <v>13.983912276</v>
+      </c>
+      <c r="DM2" t="n">
         <v>262</v>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>2 × 131</t>
         </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>1183411.91</v>
       </c>
     </row>
     <row r="3">
@@ -1869,12 +1885,18 @@
         <v>3.228971</v>
       </c>
       <c r="DL3" t="n">
+        <v>13.63565532</v>
+      </c>
+      <c r="DM3" t="n">
         <v>229</v>
       </c>
-      <c r="DM3" t="inlineStr">
+      <c r="DN3" t="inlineStr">
         <is>
           <t>229</t>
         </is>
+      </c>
+      <c r="DO3" t="n">
+        <v>835391.14</v>
       </c>
     </row>
     <row r="4">
@@ -2302,12 +2324,18 @@
         <v>2.65581841</v>
       </c>
       <c r="DL4" t="n">
+        <v>14.141475902</v>
+      </c>
+      <c r="DM4" t="n">
         <v>656</v>
       </c>
-      <c r="DM4" t="inlineStr">
+      <c r="DN4" t="inlineStr">
         <is>
           <t>2^4 × 41</t>
         </is>
+      </c>
+      <c r="DO4" t="n">
+        <v>1385367.36</v>
       </c>
     </row>
     <row r="5">
@@ -2735,12 +2763,18 @@
         <v>2.577300629</v>
       </c>
       <c r="DL5" t="n">
+        <v>13.958546783</v>
+      </c>
+      <c r="DM5" t="n">
         <v>577</v>
       </c>
-      <c r="DM5" t="inlineStr">
+      <c r="DN5" t="inlineStr">
         <is>
           <t>577</t>
         </is>
+      </c>
+      <c r="DO5" t="n">
+        <v>1153771.6</v>
       </c>
     </row>
     <row r="6">
@@ -3168,12 +3202,18 @@
         <v>3.319018949</v>
       </c>
       <c r="DL6" t="n">
+        <v>12.911058516</v>
+      </c>
+      <c r="DM6" t="n">
         <v>319</v>
       </c>
-      <c r="DM6" t="inlineStr">
+      <c r="DN6" t="inlineStr">
         <is>
           <t>11 × 29</t>
         </is>
+      </c>
+      <c r="DO6" t="n">
+        <v>404763.62</v>
       </c>
     </row>
     <row r="7">
@@ -3601,12 +3641,18 @@
         <v>3.203676606</v>
       </c>
       <c r="DL7" t="n">
+        <v>13.205727019</v>
+      </c>
+      <c r="DM7" t="n">
         <v>204</v>
       </c>
-      <c r="DM7" t="inlineStr">
+      <c r="DN7" t="inlineStr">
         <is>
           <t>2^2 × 3 × 17</t>
         </is>
+      </c>
+      <c r="DO7" t="n">
+        <v>543468.5</v>
       </c>
     </row>
     <row r="8">
@@ -4034,12 +4080,18 @@
         <v>2.752534</v>
       </c>
       <c r="DL8" t="n">
+        <v>14.137759032</v>
+      </c>
+      <c r="DM8" t="n">
         <v>753</v>
       </c>
-      <c r="DM8" t="inlineStr">
+      <c r="DN8" t="inlineStr">
         <is>
           <t>3 × 251</t>
         </is>
+      </c>
+      <c r="DO8" t="n">
+        <v>1380227.68</v>
       </c>
     </row>
     <row r="9">
@@ -4459,12 +4511,18 @@
         <v>2.264608702</v>
       </c>
       <c r="DL9" t="n">
+        <v>13.001657832</v>
+      </c>
+      <c r="DM9" t="n">
         <v>265</v>
       </c>
-      <c r="DM9" t="inlineStr">
+      <c r="DN9" t="inlineStr">
         <is>
           <t>5 × 53</t>
         </is>
+      </c>
+      <c r="DO9" t="n">
+        <v>443147.45</v>
       </c>
     </row>
     <row r="10">
@@ -4892,12 +4950,18 @@
         <v>3.214997764</v>
       </c>
       <c r="DL10" t="n">
+        <v>12.740828395</v>
+      </c>
+      <c r="DM10" t="n">
         <v>215</v>
       </c>
-      <c r="DM10" t="inlineStr">
+      <c r="DN10" t="inlineStr">
         <is>
           <t>5 × 43</t>
         </is>
+      </c>
+      <c r="DO10" t="n">
+        <v>341406.25</v>
       </c>
     </row>
     <row r="11">
@@ -5325,12 +5389,18 @@
         <v>3.37000025</v>
       </c>
       <c r="DL11" t="n">
+        <v>12.943300281</v>
+      </c>
+      <c r="DM11" t="n">
         <v>370</v>
       </c>
-      <c r="DM11" t="inlineStr">
+      <c r="DN11" t="inlineStr">
         <is>
           <t>2 × 5 × 37</t>
         </is>
+      </c>
+      <c r="DO11" t="n">
+        <v>418026.57</v>
       </c>
     </row>
     <row r="12">
@@ -5758,12 +5828,18 @@
         <v>3.149786103</v>
       </c>
       <c r="DL12" t="n">
+        <v>13.383814579</v>
+      </c>
+      <c r="DM12" t="n">
         <v>150</v>
       </c>
-      <c r="DM12" t="inlineStr">
+      <c r="DN12" t="inlineStr">
         <is>
           <t>2 × 3 × 5^2</t>
         </is>
+      </c>
+      <c r="DO12" t="n">
+        <v>649406.78</v>
       </c>
     </row>
     <row r="13">
@@ -6191,12 +6267,18 @@
         <v>3.32456625</v>
       </c>
       <c r="DL13" t="n">
+        <v>12.564449676</v>
+      </c>
+      <c r="DM13" t="n">
         <v>325</v>
       </c>
-      <c r="DM13" t="inlineStr">
+      <c r="DN13" t="inlineStr">
         <is>
           <t>5^2 × 13</t>
         </is>
+      </c>
+      <c r="DO13" t="n">
+        <v>286201.01</v>
       </c>
     </row>
     <row r="14">
@@ -6616,12 +6698,18 @@
         <v>2.88658025</v>
       </c>
       <c r="DL14" t="n">
+        <v>13.197550841</v>
+      </c>
+      <c r="DM14" t="n">
         <v>887</v>
       </c>
-      <c r="DM14" t="inlineStr">
+      <c r="DN14" t="inlineStr">
         <is>
           <t>887</t>
         </is>
+      </c>
+      <c r="DO14" t="n">
+        <v>539043.12</v>
       </c>
     </row>
     <row r="15">
@@ -7049,12 +7137,18 @@
         <v>3.287393195</v>
       </c>
       <c r="DL15" t="n">
+        <v>12.719494079</v>
+      </c>
+      <c r="DM15" t="n">
         <v>287</v>
       </c>
-      <c r="DM15" t="inlineStr">
+      <c r="DN15" t="inlineStr">
         <is>
           <t>7 × 41</t>
         </is>
+      </c>
+      <c r="DO15" t="n">
+        <v>334199.73</v>
       </c>
     </row>
     <row r="16">
@@ -7482,12 +7576,18 @@
         <v>2.724801298</v>
       </c>
       <c r="DL16" t="n">
+        <v>14.575236608</v>
+      </c>
+      <c r="DM16" t="n">
         <v>725</v>
       </c>
-      <c r="DM16" t="inlineStr">
+      <c r="DN16" t="inlineStr">
         <is>
           <t>5^2 × 29</t>
         </is>
+      </c>
+      <c r="DO16" t="n">
+        <v>2137690.52</v>
       </c>
     </row>
     <row r="17">
@@ -7915,12 +8015,18 @@
         <v>2.322328451</v>
       </c>
       <c r="DL17" t="n">
+        <v>13.788066175</v>
+      </c>
+      <c r="DM17" t="n">
         <v>322</v>
       </c>
-      <c r="DM17" t="inlineStr">
+      <c r="DN17" t="inlineStr">
         <is>
           <t>2 × 7 × 23</t>
         </is>
+      </c>
+      <c r="DO17" t="n">
+        <v>972928.79</v>
       </c>
     </row>
     <row r="18">
@@ -8344,12 +8450,18 @@
         <v>3.009548583</v>
       </c>
       <c r="DL18" t="n">
+        <v>13.991312373</v>
+      </c>
+      <c r="DM18" t="n">
         <v>10</v>
       </c>
-      <c r="DM18" t="inlineStr">
+      <c r="DN18" t="inlineStr">
         <is>
           <t>2 × 5</t>
         </is>
+      </c>
+      <c r="DO18" t="n">
+        <v>1192201.76</v>
       </c>
     </row>
     <row r="19">
@@ -8773,12 +8885,18 @@
         <v>3.06549989</v>
       </c>
       <c r="DL19" t="n">
+        <v>13.746590209</v>
+      </c>
+      <c r="DM19" t="n">
         <v>65</v>
       </c>
-      <c r="DM19" t="inlineStr">
+      <c r="DN19" t="inlineStr">
         <is>
           <t>5 × 13</t>
         </is>
+      </c>
+      <c r="DO19" t="n">
+        <v>933401.02</v>
       </c>
     </row>
     <row r="20">
@@ -9198,12 +9316,18 @@
         <v>3.172525388</v>
       </c>
       <c r="DL20" t="n">
+        <v>12.794883453</v>
+      </c>
+      <c r="DM20" t="n">
         <v>173</v>
       </c>
-      <c r="DM20" t="inlineStr">
+      <c r="DN20" t="inlineStr">
         <is>
           <t>173</t>
         </is>
+      </c>
+      <c r="DO20" t="n">
+        <v>360368.88</v>
       </c>
     </row>
     <row r="21">
@@ -9631,12 +9755,18 @@
         <v>2.31046849</v>
       </c>
       <c r="DL21" t="n">
+        <v>13.134523651</v>
+      </c>
+      <c r="DM21" t="n">
         <v>310</v>
       </c>
-      <c r="DM21" t="inlineStr">
+      <c r="DN21" t="inlineStr">
         <is>
           <t>2 × 5 × 31</t>
         </is>
+      </c>
+      <c r="DO21" t="n">
+        <v>506117.26</v>
       </c>
     </row>
     <row r="22">
@@ -10064,12 +10194,18 @@
         <v>2.200339391</v>
       </c>
       <c r="DL22" t="n">
+        <v>14.060188323</v>
+      </c>
+      <c r="DM22" t="n">
         <v>200</v>
       </c>
-      <c r="DM22" t="inlineStr">
+      <c r="DN22" t="inlineStr">
         <is>
           <t>2^3 × 5^2</t>
         </is>
+      </c>
+      <c r="DO22" t="n">
+        <v>1277209.69</v>
       </c>
     </row>
     <row r="23">
@@ -10497,9 +10633,15 @@
         <v>3.001321451</v>
       </c>
       <c r="DL23" t="n">
+        <v>14.060719612</v>
+      </c>
+      <c r="DM23" t="n">
         <v>1</v>
       </c>
-      <c r="DM23" t="inlineStr"/>
+      <c r="DN23" t="inlineStr"/>
+      <c r="DO23" t="n">
+        <v>1277888.43</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10918,12 +11060,18 @@
         <v>2.973607563</v>
       </c>
       <c r="DL24" t="n">
+        <v>13.399544002</v>
+      </c>
+      <c r="DM24" t="n">
         <v>974</v>
       </c>
-      <c r="DM24" t="inlineStr">
+      <c r="DN24" t="inlineStr">
         <is>
           <t>2 × 487</t>
         </is>
+      </c>
+      <c r="DO24" t="n">
+        <v>659702.33</v>
       </c>
     </row>
     <row r="25">
@@ -11343,12 +11491,18 @@
         <v>3.23141066</v>
       </c>
       <c r="DL25" t="n">
+        <v>12.578676933</v>
+      </c>
+      <c r="DM25" t="n">
         <v>231</v>
       </c>
-      <c r="DM25" t="inlineStr">
+      <c r="DN25" t="inlineStr">
         <is>
           <t>3 × 7 × 11</t>
         </is>
+      </c>
+      <c r="DO25" t="n">
+        <v>290301.97</v>
       </c>
     </row>
     <row r="26">
@@ -11764,12 +11918,18 @@
         <v>3.187826063</v>
       </c>
       <c r="DL26" t="n">
+        <v>12.116426158</v>
+      </c>
+      <c r="DM26" t="n">
         <v>188</v>
       </c>
-      <c r="DM26" t="inlineStr">
+      <c r="DN26" t="inlineStr">
         <is>
           <t>2^2 × 47</t>
         </is>
+      </c>
+      <c r="DO26" t="n">
+        <v>182850.87</v>
       </c>
     </row>
     <row r="27">
@@ -12197,12 +12357,18 @@
         <v>3.12303156</v>
       </c>
       <c r="DL27" t="n">
+        <v>11.990792432</v>
+      </c>
+      <c r="DM27" t="n">
         <v>123</v>
       </c>
-      <c r="DM27" t="inlineStr">
+      <c r="DN27" t="inlineStr">
         <is>
           <t>3 × 41</t>
         </is>
+      </c>
+      <c r="DO27" t="n">
+        <v>161263.09</v>
       </c>
     </row>
     <row r="28">
@@ -12630,12 +12796,18 @@
         <v>3.224337213</v>
       </c>
       <c r="DL28" t="n">
+        <v>12.990817022</v>
+      </c>
+      <c r="DM28" t="n">
         <v>224</v>
       </c>
-      <c r="DM28" t="inlineStr">
+      <c r="DN28" t="inlineStr">
         <is>
           <t>2^5 × 7</t>
         </is>
+      </c>
+      <c r="DO28" t="n">
+        <v>438369.32</v>
       </c>
     </row>
     <row r="29">
@@ -13059,12 +13231,18 @@
         <v>2.937612831</v>
       </c>
       <c r="DL29" t="n">
+        <v>13.563943178</v>
+      </c>
+      <c r="DM29" t="n">
         <v>938</v>
       </c>
-      <c r="DM29" t="inlineStr">
+      <c r="DN29" t="inlineStr">
         <is>
           <t>2 × 7 × 67</t>
         </is>
+      </c>
+      <c r="DO29" t="n">
+        <v>777581.0600000001</v>
       </c>
     </row>
     <row r="30">
@@ -13492,12 +13670,18 @@
         <v>3.149011017</v>
       </c>
       <c r="DL30" t="n">
+        <v>11.803207853</v>
+      </c>
+      <c r="DM30" t="n">
         <v>149</v>
       </c>
-      <c r="DM30" t="inlineStr">
+      <c r="DN30" t="inlineStr">
         <is>
           <t>149</t>
         </is>
+      </c>
+      <c r="DO30" t="n">
+        <v>133680.49</v>
       </c>
     </row>
     <row r="31">
@@ -13921,12 +14105,18 @@
         <v>2.721570063</v>
       </c>
       <c r="DL31" t="n">
+        <v>14.431784296</v>
+      </c>
+      <c r="DM31" t="n">
         <v>722</v>
       </c>
-      <c r="DM31" t="inlineStr">
+      <c r="DN31" t="inlineStr">
         <is>
           <t>2 × 19^2</t>
         </is>
+      </c>
+      <c r="DO31" t="n">
+        <v>1852014.08</v>
       </c>
     </row>
     <row r="32">
@@ -14346,12 +14536,18 @@
         <v>3.261965165</v>
       </c>
       <c r="DL32" t="n">
+        <v>12.393898377</v>
+      </c>
+      <c r="DM32" t="n">
         <v>262</v>
       </c>
-      <c r="DM32" t="inlineStr">
+      <c r="DN32" t="inlineStr">
         <is>
           <t>2 × 131</t>
         </is>
+      </c>
+      <c r="DO32" t="n">
+        <v>241324.64</v>
       </c>
     </row>
     <row r="33">
@@ -14779,12 +14975,18 @@
         <v>3.060337696</v>
       </c>
       <c r="DL33" t="n">
+        <v>12.775552529</v>
+      </c>
+      <c r="DM33" t="n">
         <v>60</v>
       </c>
-      <c r="DM33" t="inlineStr">
+      <c r="DN33" t="inlineStr">
         <is>
           <t>2^2 × 3 × 5</t>
         </is>
+      </c>
+      <c r="DO33" t="n">
+        <v>353469.52</v>
       </c>
     </row>
     <row r="34">
@@ -15208,12 +15410,18 @@
         <v>3.019238608</v>
       </c>
       <c r="DL34" t="n">
+        <v>14.047644974</v>
+      </c>
+      <c r="DM34" t="n">
         <v>19</v>
       </c>
-      <c r="DM34" t="inlineStr">
+      <c r="DN34" t="inlineStr">
         <is>
           <t>19</t>
         </is>
+      </c>
+      <c r="DO34" t="n">
+        <v>1261289.25</v>
       </c>
     </row>
     <row r="35">
@@ -15629,12 +15837,18 @@
         <v>2.720224894</v>
       </c>
       <c r="DL35" t="n">
+        <v>13.349970094</v>
+      </c>
+      <c r="DM35" t="n">
         <v>720</v>
       </c>
-      <c r="DM35" t="inlineStr">
+      <c r="DN35" t="inlineStr">
         <is>
           <t>2^4 × 3^2 × 5</t>
         </is>
+      </c>
+      <c r="DO35" t="n">
+        <v>627795.71</v>
       </c>
     </row>
     <row r="36">
@@ -16054,12 +16268,18 @@
         <v>2.838282913</v>
       </c>
       <c r="DL36" t="n">
+        <v>13.629942173</v>
+      </c>
+      <c r="DM36" t="n">
         <v>838</v>
       </c>
-      <c r="DM36" t="inlineStr">
+      <c r="DN36" t="inlineStr">
         <is>
           <t>2 × 419</t>
         </is>
+      </c>
+      <c r="DO36" t="n">
+        <v>830632.03</v>
       </c>
     </row>
     <row r="37">
@@ -16483,12 +16703,18 @@
         <v>3.179936502</v>
       </c>
       <c r="DL37" t="n">
+        <v>13.783496662</v>
+      </c>
+      <c r="DM37" t="n">
         <v>180</v>
       </c>
-      <c r="DM37" t="inlineStr">
+      <c r="DN37" t="inlineStr">
         <is>
           <t>2^2 × 3^2 × 5</t>
         </is>
+      </c>
+      <c r="DO37" t="n">
+        <v>968493.12</v>
       </c>
     </row>
     <row r="38">
@@ -16912,12 +17138,18 @@
         <v>3.003545063</v>
       </c>
       <c r="DL38" t="n">
+        <v>13.129131976</v>
+      </c>
+      <c r="DM38" t="n">
         <v>4</v>
       </c>
-      <c r="DM38" t="inlineStr">
+      <c r="DN38" t="inlineStr">
         <is>
           <t>2^2</t>
         </is>
+      </c>
+      <c r="DO38" t="n">
+        <v>503395.78</v>
       </c>
     </row>
     <row r="39">
@@ -17345,12 +17577,18 @@
         <v>3.163773402</v>
       </c>
       <c r="DL39" t="n">
+        <v>13.681584597</v>
+      </c>
+      <c r="DM39" t="n">
         <v>164</v>
       </c>
-      <c r="DM39" t="inlineStr">
+      <c r="DN39" t="inlineStr">
         <is>
           <t>2^2 × 41</t>
         </is>
+      </c>
+      <c r="DO39" t="n">
+        <v>874654.8199999999</v>
       </c>
     </row>
     <row r="40">
@@ -17774,12 +18012,18 @@
         <v>3.039283285</v>
       </c>
       <c r="DL40" t="n">
+        <v>12.483906895</v>
+      </c>
+      <c r="DM40" t="n">
         <v>39</v>
       </c>
-      <c r="DM40" t="inlineStr">
+      <c r="DN40" t="inlineStr">
         <is>
           <t>3 × 13</t>
         </is>
+      </c>
+      <c r="DO40" t="n">
+        <v>264053.47</v>
       </c>
     </row>
     <row r="41">
@@ -18203,12 +18447,18 @@
         <v>2.944222201</v>
       </c>
       <c r="DL41" t="n">
+        <v>12.665024006</v>
+      </c>
+      <c r="DM41" t="n">
         <v>944</v>
       </c>
-      <c r="DM41" t="inlineStr">
+      <c r="DN41" t="inlineStr">
         <is>
           <t>2^4 × 59</t>
         </is>
+      </c>
+      <c r="DO41" t="n">
+        <v>316482.75</v>
       </c>
     </row>
     <row r="42">
@@ -18636,12 +18886,18 @@
         <v>3.051397007</v>
       </c>
       <c r="DL42" t="n">
+        <v>12.998152328</v>
+      </c>
+      <c r="DM42" t="n">
         <v>51</v>
       </c>
-      <c r="DM42" t="inlineStr">
+      <c r="DN42" t="inlineStr">
         <is>
           <t>3 × 17</t>
         </is>
+      </c>
+      <c r="DO42" t="n">
+        <v>441596.71</v>
       </c>
     </row>
     <row r="43">
@@ -19061,12 +19317,18 @@
         <v>2.998611775</v>
       </c>
       <c r="DL43" t="n">
+        <v>13.378083203</v>
+      </c>
+      <c r="DM43" t="n">
         <v>999</v>
       </c>
-      <c r="DM43" t="inlineStr">
+      <c r="DN43" t="inlineStr">
         <is>
           <t>3^3 × 37</t>
         </is>
+      </c>
+      <c r="DO43" t="n">
+        <v>645695.4300000001</v>
       </c>
     </row>
     <row r="44">
@@ -19494,12 +19756,18 @@
         <v>2.935709721</v>
       </c>
       <c r="DL44" t="n">
+        <v>13.086365897</v>
+      </c>
+      <c r="DM44" t="n">
         <v>936</v>
       </c>
-      <c r="DM44" t="inlineStr">
+      <c r="DN44" t="inlineStr">
         <is>
           <t>2^3 × 3^2 × 13</t>
         </is>
+      </c>
+      <c r="DO44" t="n">
+        <v>482321.36</v>
       </c>
     </row>
     <row r="45">
@@ -19923,12 +20191,18 @@
         <v>2.890322266</v>
       </c>
       <c r="DL45" t="n">
+        <v>13.237375151</v>
+      </c>
+      <c r="DM45" t="n">
         <v>890</v>
       </c>
-      <c r="DM45" t="inlineStr">
+      <c r="DN45" t="inlineStr">
         <is>
           <t>2 × 5 × 89</t>
         </is>
+      </c>
+      <c r="DO45" t="n">
+        <v>560943.3199999999</v>
       </c>
     </row>
     <row r="46">
@@ -20356,12 +20630,18 @@
         <v>2.707392327</v>
       </c>
       <c r="DL46" t="n">
+        <v>12.958516305</v>
+      </c>
+      <c r="DM46" t="n">
         <v>707</v>
       </c>
-      <c r="DM46" t="inlineStr">
+      <c r="DN46" t="inlineStr">
         <is>
           <t>7 × 101</t>
         </is>
+      </c>
+      <c r="DO46" t="n">
+        <v>424435.91</v>
       </c>
     </row>
     <row r="47">
@@ -20789,12 +21069,18 @@
         <v>2.565670027</v>
       </c>
       <c r="DL47" t="n">
+        <v>12.62609033</v>
+      </c>
+      <c r="DM47" t="n">
         <v>566</v>
       </c>
-      <c r="DM47" t="inlineStr">
+      <c r="DN47" t="inlineStr">
         <is>
           <t>2 × 283</t>
         </is>
+      </c>
+      <c r="DO47" t="n">
+        <v>304397.69</v>
       </c>
     </row>
     <row r="48">
@@ -21214,12 +21500,18 @@
         <v>2.55072864</v>
       </c>
       <c r="DL48" t="n">
+        <v>13.271743754</v>
+      </c>
+      <c r="DM48" t="n">
         <v>551</v>
       </c>
-      <c r="DM48" t="inlineStr">
+      <c r="DN48" t="inlineStr">
         <is>
           <t>19 × 29</t>
         </is>
+      </c>
+      <c r="DO48" t="n">
+        <v>580557.28</v>
       </c>
     </row>
     <row r="49">
@@ -21635,12 +21927,18 @@
         <v>2.644817837</v>
       </c>
       <c r="DL49" t="n">
+        <v>12.761738638</v>
+      </c>
+      <c r="DM49" t="n">
         <v>645</v>
       </c>
-      <c r="DM49" t="inlineStr">
+      <c r="DN49" t="inlineStr">
         <is>
           <t>3 × 5 × 43</t>
         </is>
+      </c>
+      <c r="DO49" t="n">
+        <v>348620.3</v>
       </c>
     </row>
     <row r="50">
@@ -22060,12 +22358,18 @@
         <v>3.016724295</v>
       </c>
       <c r="DL50" t="n">
+        <v>13.043661322</v>
+      </c>
+      <c r="DM50" t="n">
         <v>17</v>
       </c>
-      <c r="DM50" t="inlineStr">
+      <c r="DN50" t="inlineStr">
         <is>
           <t>17</t>
         </is>
+      </c>
+      <c r="DO50" t="n">
+        <v>462157.64</v>
       </c>
     </row>
     <row r="51">
@@ -22485,12 +22789,18 @@
         <v>2.32489612</v>
       </c>
       <c r="DL51" t="n">
+        <v>14.021235151</v>
+      </c>
+      <c r="DM51" t="n">
         <v>325</v>
       </c>
-      <c r="DM51" t="inlineStr">
+      <c r="DN51" t="inlineStr">
         <is>
           <t>5^2 × 13</t>
         </is>
+      </c>
+      <c r="DO51" t="n">
+        <v>1228414.84</v>
       </c>
     </row>
     <row r="52">
@@ -22906,12 +23216,18 @@
         <v>2.595786902</v>
       </c>
       <c r="DL52" t="n">
+        <v>13.591911271</v>
+      </c>
+      <c r="DM52" t="n">
         <v>596</v>
       </c>
-      <c r="DM52" t="inlineStr">
+      <c r="DN52" t="inlineStr">
         <is>
           <t>2^2 × 149</t>
         </is>
+      </c>
+      <c r="DO52" t="n">
+        <v>799635.49</v>
       </c>
     </row>
     <row r="53">
@@ -23327,12 +23643,18 @@
         <v>2.188000243</v>
       </c>
       <c r="DL53" t="n">
+        <v>13.749115244</v>
+      </c>
+      <c r="DM53" t="n">
         <v>188</v>
       </c>
-      <c r="DM53" t="inlineStr">
+      <c r="DN53" t="inlineStr">
         <is>
           <t>2^2 × 47</t>
         </is>
+      </c>
+      <c r="DO53" t="n">
+        <v>935760.87</v>
       </c>
     </row>
     <row r="54">
@@ -23748,12 +24070,18 @@
         <v>2.689071803</v>
       </c>
       <c r="DL54" t="n">
+        <v>13.368128849</v>
+      </c>
+      <c r="DM54" t="n">
         <v>689</v>
       </c>
-      <c r="DM54" t="inlineStr">
+      <c r="DN54" t="inlineStr">
         <is>
           <t>13 × 53</t>
         </is>
+      </c>
+      <c r="DO54" t="n">
+        <v>639299.84</v>
       </c>
     </row>
     <row r="55">
@@ -24173,12 +24501,18 @@
         <v>2.007452251</v>
       </c>
       <c r="DL55" t="n">
+        <v>12.691817108</v>
+      </c>
+      <c r="DM55" t="n">
         <v>7</v>
       </c>
-      <c r="DM55" t="inlineStr">
+      <c r="DN55" t="inlineStr">
         <is>
           <t>7</t>
         </is>
+      </c>
+      <c r="DO55" t="n">
+        <v>325076.92</v>
       </c>
     </row>
     <row r="56">
@@ -24606,12 +24940,18 @@
         <v>3.062042016</v>
       </c>
       <c r="DL56" t="n">
+        <v>13.572837812</v>
+      </c>
+      <c r="DM56" t="n">
         <v>62</v>
       </c>
-      <c r="DM56" t="inlineStr">
+      <c r="DN56" t="inlineStr">
         <is>
           <t>2 × 31</t>
         </is>
+      </c>
+      <c r="DO56" t="n">
+        <v>784528.21</v>
       </c>
     </row>
     <row r="57">
@@ -25031,12 +25371,18 @@
         <v>2.776444516</v>
       </c>
       <c r="DL57" t="n">
+        <v>13.97162511</v>
+      </c>
+      <c r="DM57" t="n">
         <v>776</v>
       </c>
-      <c r="DM57" t="inlineStr">
+      <c r="DN57" t="inlineStr">
         <is>
           <t>2^3 × 97</t>
         </is>
+      </c>
+      <c r="DO57" t="n">
+        <v>1168960.1</v>
       </c>
     </row>
     <row r="58">
@@ -25452,12 +25798,18 @@
         <v>3.10345764</v>
       </c>
       <c r="DL58" t="n">
+        <v>12.821727012</v>
+      </c>
+      <c r="DM58" t="n">
         <v>103</v>
       </c>
-      <c r="DM58" t="inlineStr">
+      <c r="DN58" t="inlineStr">
         <is>
           <t>103</t>
         </is>
+      </c>
+      <c r="DO58" t="n">
+        <v>370173.47</v>
       </c>
     </row>
     <row r="59">
@@ -25881,12 +26233,18 @@
         <v>2.949836713</v>
       </c>
       <c r="DL59" t="n">
+        <v>14.02091151</v>
+      </c>
+      <c r="DM59" t="n">
         <v>950</v>
       </c>
-      <c r="DM59" t="inlineStr">
+      <c r="DN59" t="inlineStr">
         <is>
           <t>2 × 5^2 × 19</t>
         </is>
+      </c>
+      <c r="DO59" t="n">
+        <v>1228017.34</v>
       </c>
     </row>
     <row r="60">
@@ -26310,12 +26668,18 @@
         <v>2.780347623</v>
       </c>
       <c r="DL60" t="n">
+        <v>13.969996765</v>
+      </c>
+      <c r="DM60" t="n">
         <v>780</v>
       </c>
-      <c r="DM60" t="inlineStr">
+      <c r="DN60" t="inlineStr">
         <is>
           <t>2^2 × 3 × 5 × 13</t>
         </is>
+      </c>
+      <c r="DO60" t="n">
+        <v>1167058.18</v>
       </c>
     </row>
     <row r="61">
@@ -26743,12 +27107,18 @@
         <v>2.987523674</v>
       </c>
       <c r="DL61" t="n">
+        <v>13.090362237</v>
+      </c>
+      <c r="DM61" t="n">
         <v>988</v>
       </c>
-      <c r="DM61" t="inlineStr">
+      <c r="DN61" t="inlineStr">
         <is>
           <t>2^2 × 13 × 19</t>
         </is>
+      </c>
+      <c r="DO61" t="n">
+        <v>484252.74</v>
       </c>
     </row>
     <row r="62">
@@ -27164,12 +27534,18 @@
         <v>2.813001723</v>
       </c>
       <c r="DL62" t="n">
+        <v>12.423874655</v>
+      </c>
+      <c r="DM62" t="n">
         <v>813</v>
       </c>
-      <c r="DM62" t="inlineStr">
+      <c r="DN62" t="inlineStr">
         <is>
           <t>3 × 271</t>
         </is>
+      </c>
+      <c r="DO62" t="n">
+        <v>248668.17</v>
       </c>
     </row>
     <row r="63">
@@ -27589,12 +27965,18 @@
         <v>2.848684717</v>
       </c>
       <c r="DL63" t="n">
+        <v>13.687719572</v>
+      </c>
+      <c r="DM63" t="n">
         <v>849</v>
       </c>
-      <c r="DM63" t="inlineStr">
+      <c r="DN63" t="inlineStr">
         <is>
           <t>3 × 283</t>
         </is>
+      </c>
+      <c r="DO63" t="n">
+        <v>880037.3</v>
       </c>
     </row>
     <row r="64">
@@ -28010,12 +28392,18 @@
         <v>2.953178316</v>
       </c>
       <c r="DL64" t="n">
+        <v>13.355790795</v>
+      </c>
+      <c r="DM64" t="n">
         <v>953</v>
       </c>
-      <c r="DM64" t="inlineStr">
+      <c r="DN64" t="inlineStr">
         <is>
           <t>953</t>
         </is>
+      </c>
+      <c r="DO64" t="n">
+        <v>631460.58</v>
       </c>
     </row>
     <row r="65">
@@ -28439,12 +28827,18 @@
         <v>2.83914969</v>
       </c>
       <c r="DL65" t="n">
+        <v>14.062706109</v>
+      </c>
+      <c r="DM65" t="n">
         <v>839</v>
       </c>
-      <c r="DM65" t="inlineStr">
+      <c r="DN65" t="inlineStr">
         <is>
           <t>839</t>
         </is>
+      </c>
+      <c r="DO65" t="n">
+        <v>1280429.48</v>
       </c>
     </row>
     <row r="66">
@@ -28868,12 +29262,18 @@
         <v>2.596565884</v>
       </c>
       <c r="DL66" t="n">
+        <v>13.474160408</v>
+      </c>
+      <c r="DM66" t="n">
         <v>597</v>
       </c>
-      <c r="DM66" t="inlineStr">
+      <c r="DN66" t="inlineStr">
         <is>
           <t>3 × 199</t>
         </is>
+      </c>
+      <c r="DO66" t="n">
+        <v>710809.97</v>
       </c>
     </row>
     <row r="67">
@@ -29297,12 +29697,18 @@
         <v>2.556162958</v>
       </c>
       <c r="DL67" t="n">
+        <v>13.871679993</v>
+      </c>
+      <c r="DM67" t="n">
         <v>556</v>
       </c>
-      <c r="DM67" t="inlineStr">
+      <c r="DN67" t="inlineStr">
         <is>
           <t>2^2 × 139</t>
         </is>
+      </c>
+      <c r="DO67" t="n">
+        <v>1057776.89</v>
       </c>
     </row>
     <row r="68">
@@ -29718,12 +30124,18 @@
         <v>2.687333006</v>
       </c>
       <c r="DL68" t="n">
+        <v>13.474997079</v>
+      </c>
+      <c r="DM68" t="n">
         <v>687</v>
       </c>
-      <c r="DM68" t="inlineStr">
+      <c r="DN68" t="inlineStr">
         <is>
           <t>3 × 229</t>
         </is>
+      </c>
+      <c r="DO68" t="n">
+        <v>711404.9399999999</v>
       </c>
     </row>
     <row r="69">
@@ -30143,12 +30555,18 @@
         <v>2.603148491</v>
       </c>
       <c r="DL69" t="n">
+        <v>13.559863543</v>
+      </c>
+      <c r="DM69" t="n">
         <v>603</v>
       </c>
-      <c r="DM69" t="inlineStr">
+      <c r="DN69" t="inlineStr">
         <is>
           <t>3^2 × 67</t>
         </is>
+      </c>
+      <c r="DO69" t="n">
+        <v>774415.28</v>
       </c>
     </row>
     <row r="70">
@@ -30564,12 +30982,18 @@
         <v>2.47160641</v>
       </c>
       <c r="DL70" t="n">
+        <v>13.105262711</v>
+      </c>
+      <c r="DM70" t="n">
         <v>472</v>
       </c>
-      <c r="DM70" t="inlineStr">
+      <c r="DN70" t="inlineStr">
         <is>
           <t>2^3 × 59</t>
         </is>
+      </c>
+      <c r="DO70" t="n">
+        <v>491522.36</v>
       </c>
     </row>
     <row r="71">
@@ -30997,12 +31421,18 @@
         <v>1.900970274</v>
       </c>
       <c r="DL71" t="n">
+        <v>12.984714721</v>
+      </c>
+      <c r="DM71" t="n">
         <v>901</v>
       </c>
-      <c r="DM71" t="inlineStr">
+      <c r="DN71" t="inlineStr">
         <is>
           <t>17 × 53</t>
         </is>
+      </c>
+      <c r="DO71" t="n">
+        <v>435702.4</v>
       </c>
     </row>
     <row r="72">
@@ -31422,12 +31852,18 @@
         <v>2.502798688</v>
       </c>
       <c r="DL72" t="n">
+        <v>11.951656148</v>
+      </c>
+      <c r="DM72" t="n">
         <v>503</v>
       </c>
-      <c r="DM72" t="inlineStr">
+      <c r="DN72" t="inlineStr">
         <is>
           <t>503</t>
         </is>
+      </c>
+      <c r="DO72" t="n">
+        <v>155073.76</v>
       </c>
     </row>
     <row r="73">
@@ -31851,12 +32287,18 @@
         <v>1.998126</v>
       </c>
       <c r="DL73" t="n">
+        <v>14.422615262</v>
+      </c>
+      <c r="DM73" t="n">
         <v>998</v>
       </c>
-      <c r="DM73" t="inlineStr">
+      <c r="DN73" t="inlineStr">
         <is>
           <t>2 × 499</t>
         </is>
+      </c>
+      <c r="DO73" t="n">
+        <v>1835110.51</v>
       </c>
     </row>
     <row r="74">
@@ -32276,12 +32718,18 @@
         <v>2.932859066</v>
       </c>
       <c r="DL74" t="n">
+        <v>12.579902427</v>
+      </c>
+      <c r="DM74" t="n">
         <v>933</v>
       </c>
-      <c r="DM74" t="inlineStr">
+      <c r="DN74" t="inlineStr">
         <is>
           <t>3 × 311</t>
         </is>
+      </c>
+      <c r="DO74" t="n">
+        <v>290657.95</v>
       </c>
     </row>
     <row r="75">
@@ -32705,12 +33153,18 @@
         <v>2.140585</v>
       </c>
       <c r="DL75" t="n">
+        <v>12.993322059</v>
+      </c>
+      <c r="DM75" t="n">
         <v>141</v>
       </c>
-      <c r="DM75" t="inlineStr">
+      <c r="DN75" t="inlineStr">
         <is>
           <t>3 × 47</t>
         </is>
+      </c>
+      <c r="DO75" t="n">
+        <v>439468.82</v>
       </c>
     </row>
     <row r="76">
@@ -33134,12 +33588,18 @@
         <v>2.480943141</v>
       </c>
       <c r="DL76" t="n">
+        <v>13.534997353</v>
+      </c>
+      <c r="DM76" t="n">
         <v>481</v>
       </c>
-      <c r="DM76" t="inlineStr">
+      <c r="DN76" t="inlineStr">
         <is>
           <t>13 × 37</t>
         </is>
+      </c>
+      <c r="DO76" t="n">
+        <v>755395.97</v>
       </c>
     </row>
     <row r="77">
@@ -33555,12 +34015,18 @@
         <v>2.082076532</v>
       </c>
       <c r="DL77" t="n">
+        <v>12.584377053</v>
+      </c>
+      <c r="DM77" t="n">
         <v>82</v>
       </c>
-      <c r="DM77" t="inlineStr">
+      <c r="DN77" t="inlineStr">
         <is>
           <t>2 × 41</t>
         </is>
+      </c>
+      <c r="DO77" t="n">
+        <v>291961.45</v>
       </c>
     </row>
     <row r="78">
@@ -33988,12 +34454,18 @@
         <v>3.047450464</v>
       </c>
       <c r="DL78" t="n">
+        <v>14.383252941</v>
+      </c>
+      <c r="DM78" t="n">
         <v>47</v>
       </c>
-      <c r="DM78" t="inlineStr">
+      <c r="DN78" t="inlineStr">
         <is>
           <t>47</t>
         </is>
+      </c>
+      <c r="DO78" t="n">
+        <v>1764279.48</v>
       </c>
     </row>
     <row r="79">
@@ -34417,12 +34889,18 @@
         <v>2.915187782</v>
       </c>
       <c r="DL79" t="n">
+        <v>12.765804117</v>
+      </c>
+      <c r="DM79" t="n">
         <v>915</v>
       </c>
-      <c r="DM79" t="inlineStr">
+      <c r="DN79" t="inlineStr">
         <is>
           <t>3 × 5 × 61</t>
         </is>
+      </c>
+      <c r="DO79" t="n">
+        <v>350040.49</v>
       </c>
     </row>
     <row r="80">
@@ -34838,12 +35316,18 @@
         <v>2.794945303</v>
       </c>
       <c r="DL80" t="n">
+        <v>13.322590854</v>
+      </c>
+      <c r="DM80" t="n">
         <v>795</v>
       </c>
-      <c r="DM80" t="inlineStr">
+      <c r="DN80" t="inlineStr">
         <is>
           <t>3 × 5 × 53</t>
         </is>
+      </c>
+      <c r="DO80" t="n">
+        <v>610840.3199999999</v>
       </c>
     </row>
     <row r="81">
@@ -35259,12 +35743,18 @@
         <v>2.557167789</v>
       </c>
       <c r="DL81" t="n">
+        <v>13.56673593</v>
+      </c>
+      <c r="DM81" t="n">
         <v>557</v>
       </c>
-      <c r="DM81" t="inlineStr">
+      <c r="DN81" t="inlineStr">
         <is>
           <t>557</t>
         </is>
+      </c>
+      <c r="DO81" t="n">
+        <v>779755.6899999999</v>
       </c>
     </row>
     <row r="82">
@@ -35688,12 +36178,18 @@
         <v>2.786888063</v>
       </c>
       <c r="DL82" t="n">
+        <v>13.343591627</v>
+      </c>
+      <c r="DM82" t="n">
         <v>787</v>
       </c>
-      <c r="DM82" t="inlineStr">
+      <c r="DN82" t="inlineStr">
         <is>
           <t>787</t>
         </is>
+      </c>
+      <c r="DO82" t="n">
+        <v>623804.08</v>
       </c>
     </row>
     <row r="83">
@@ -36109,12 +36605,18 @@
         <v>2.965635951</v>
       </c>
       <c r="DL83" t="n">
+        <v>12.772711788</v>
+      </c>
+      <c r="DM83" t="n">
         <v>966</v>
       </c>
-      <c r="DM83" t="inlineStr">
+      <c r="DN83" t="inlineStr">
         <is>
           <t>2 × 3 × 7 × 23</t>
         </is>
+      </c>
+      <c r="DO83" t="n">
+        <v>352466.83</v>
       </c>
     </row>
     <row r="84">
@@ -36534,12 +37036,18 @@
         <v>2.76433153</v>
       </c>
       <c r="DL84" t="n">
+        <v>13.531035944</v>
+      </c>
+      <c r="DM84" t="n">
         <v>764</v>
       </c>
-      <c r="DM84" t="inlineStr">
+      <c r="DN84" t="inlineStr">
         <is>
           <t>2^2 × 191</t>
         </is>
+      </c>
+      <c r="DO84" t="n">
+        <v>752409.46</v>
       </c>
     </row>
     <row r="85">
@@ -36959,12 +37467,18 @@
         <v>2.771668379</v>
       </c>
       <c r="DL85" t="n">
+        <v>14.203778255</v>
+      </c>
+      <c r="DM85" t="n">
         <v>772</v>
       </c>
-      <c r="DM85" t="inlineStr">
+      <c r="DN85" t="inlineStr">
         <is>
           <t>2^2 × 193</t>
         </is>
+      </c>
+      <c r="DO85" t="n">
+        <v>1474424.43</v>
       </c>
     </row>
     <row r="86">
@@ -37384,12 +37898,18 @@
         <v>2.832605119</v>
       </c>
       <c r="DL86" t="n">
+        <v>13.42991975</v>
+      </c>
+      <c r="DM86" t="n">
         <v>833</v>
       </c>
-      <c r="DM86" t="inlineStr">
+      <c r="DN86" t="inlineStr">
         <is>
           <t>7^2 × 17</t>
         </is>
+      </c>
+      <c r="DO86" t="n">
+        <v>680048.74</v>
       </c>
     </row>
     <row r="87">
@@ -37817,12 +38337,18 @@
         <v>2.84156932</v>
       </c>
       <c r="DL87" t="n">
+        <v>13.928501467</v>
+      </c>
+      <c r="DM87" t="n">
         <v>842</v>
       </c>
-      <c r="DM87" t="inlineStr">
+      <c r="DN87" t="inlineStr">
         <is>
           <t>2 × 421</t>
         </is>
+      </c>
+      <c r="DO87" t="n">
+        <v>1119621.75</v>
       </c>
     </row>
     <row r="88">
@@ -38250,12 +38776,18 @@
         <v>2.645334476</v>
       </c>
       <c r="DL88" t="n">
+        <v>13.715161758</v>
+      </c>
+      <c r="DM88" t="n">
         <v>645</v>
       </c>
-      <c r="DM88" t="inlineStr">
+      <c r="DN88" t="inlineStr">
         <is>
           <t>3 × 5 × 43</t>
         </is>
+      </c>
+      <c r="DO88" t="n">
+        <v>904521.87</v>
       </c>
     </row>
     <row r="89">
@@ -38683,12 +39215,18 @@
         <v>3.047025233</v>
       </c>
       <c r="DL89" t="n">
+        <v>13.422054928</v>
+      </c>
+      <c r="DM89" t="n">
         <v>47</v>
       </c>
-      <c r="DM89" t="inlineStr">
+      <c r="DN89" t="inlineStr">
         <is>
           <t>47</t>
         </is>
+      </c>
+      <c r="DO89" t="n">
+        <v>674721.25</v>
       </c>
     </row>
     <row r="90">
@@ -39104,12 +39642,18 @@
         <v>2.992422031</v>
       </c>
       <c r="DL90" t="n">
+        <v>13.275296358</v>
+      </c>
+      <c r="DM90" t="n">
         <v>992</v>
       </c>
-      <c r="DM90" t="inlineStr">
+      <c r="DN90" t="inlineStr">
         <is>
           <t>2^5 × 31</t>
         </is>
+      </c>
+      <c r="DO90" t="n">
+        <v>582623.4399999999</v>
       </c>
     </row>
     <row r="91">
@@ -39525,12 +40069,18 @@
         <v>3.07972509</v>
       </c>
       <c r="DL91" t="n">
+        <v>12.284305391</v>
+      </c>
+      <c r="DM91" t="n">
         <v>80</v>
       </c>
-      <c r="DM91" t="inlineStr">
+      <c r="DN91" t="inlineStr">
         <is>
           <t>2^4 × 5</t>
         </is>
+      </c>
+      <c r="DO91" t="n">
+        <v>216274.86</v>
       </c>
     </row>
     <row r="92">
@@ -39950,12 +40500,18 @@
         <v>3.149004875</v>
       </c>
       <c r="DL92" t="n">
+        <v>13.241525629</v>
+      </c>
+      <c r="DM92" t="n">
         <v>149</v>
       </c>
-      <c r="DM92" t="inlineStr">
+      <c r="DN92" t="inlineStr">
         <is>
           <t>149</t>
         </is>
+      </c>
+      <c r="DO92" t="n">
+        <v>563276.34</v>
       </c>
     </row>
     <row r="93">
@@ -40375,12 +40931,18 @@
         <v>2.94543225</v>
       </c>
       <c r="DL93" t="n">
+        <v>13.63057227</v>
+      </c>
+      <c r="DM93" t="n">
         <v>945</v>
       </c>
-      <c r="DM93" t="inlineStr">
+      <c r="DN93" t="inlineStr">
         <is>
           <t>3^3 × 5 × 7</t>
         </is>
+      </c>
+      <c r="DO93" t="n">
+        <v>831155.5699999999</v>
       </c>
     </row>
     <row r="94">
@@ -40796,12 +41358,18 @@
         <v>2.965099303</v>
       </c>
       <c r="DL94" t="n">
+        <v>13.387033421</v>
+      </c>
+      <c r="DM94" t="n">
         <v>965</v>
       </c>
-      <c r="DM94" t="inlineStr">
+      <c r="DN94" t="inlineStr">
         <is>
           <t>5 × 193</t>
         </is>
+      </c>
+      <c r="DO94" t="n">
+        <v>651500.49</v>
       </c>
     </row>
     <row r="95">
@@ -41229,12 +41797,18 @@
         <v>2.932140142</v>
       </c>
       <c r="DL95" t="n">
+        <v>12.740619042</v>
+      </c>
+      <c r="DM95" t="n">
         <v>932</v>
       </c>
-      <c r="DM95" t="inlineStr">
+      <c r="DN95" t="inlineStr">
         <is>
           <t>2^2 × 233</t>
         </is>
+      </c>
+      <c r="DO95" t="n">
+        <v>341334.78</v>
       </c>
     </row>
     <row r="96">
@@ -41650,12 +42224,18 @@
         <v>2.747422214</v>
       </c>
       <c r="DL96" t="n">
+        <v>13.377858609</v>
+      </c>
+      <c r="DM96" t="n">
         <v>747</v>
       </c>
-      <c r="DM96" t="inlineStr">
+      <c r="DN96" t="inlineStr">
         <is>
           <t>3^2 × 83</t>
         </is>
+      </c>
+      <c r="DO96" t="n">
+        <v>645550.4300000001</v>
       </c>
     </row>
     <row r="97">
@@ -42079,12 +42659,18 @@
         <v>3.10465941</v>
       </c>
       <c r="DL97" t="n">
+        <v>12.539745278</v>
+      </c>
+      <c r="DM97" t="n">
         <v>105</v>
       </c>
-      <c r="DM97" t="inlineStr">
+      <c r="DN97" t="inlineStr">
         <is>
           <t>3 × 5 × 7</t>
         </is>
+      </c>
+      <c r="DO97" t="n">
+        <v>279217.21</v>
       </c>
     </row>
     <row r="98">
@@ -42508,12 +43094,18 @@
         <v>2.857898062</v>
       </c>
       <c r="DL98" t="n">
+        <v>13.515500525</v>
+      </c>
+      <c r="DM98" t="n">
         <v>858</v>
       </c>
-      <c r="DM98" t="inlineStr">
+      <c r="DN98" t="inlineStr">
         <is>
           <t>2 × 3 × 11 × 13</t>
         </is>
+      </c>
+      <c r="DO98" t="n">
+        <v>740810.79</v>
       </c>
     </row>
     <row r="99">
@@ -42929,12 +43521,18 @@
         <v>2.635621353</v>
       </c>
       <c r="DL99" t="n">
+        <v>14.222164791</v>
+      </c>
+      <c r="DM99" t="n">
         <v>636</v>
       </c>
-      <c r="DM99" t="inlineStr">
+      <c r="DN99" t="inlineStr">
         <is>
           <t>2^2 × 3 × 53</t>
         </is>
+      </c>
+      <c r="DO99" t="n">
+        <v>1501784.75</v>
       </c>
     </row>
     <row r="100">
@@ -43350,12 +43948,18 @@
         <v>2.872295131</v>
       </c>
       <c r="DL100" t="n">
+        <v>12.625038957</v>
+      </c>
+      <c r="DM100" t="n">
         <v>872</v>
       </c>
-      <c r="DM100" t="inlineStr">
+      <c r="DN100" t="inlineStr">
         <is>
           <t>2^3 × 109</t>
         </is>
+      </c>
+      <c r="DO100" t="n">
+        <v>304077.83</v>
       </c>
     </row>
     <row r="101">
@@ -43771,12 +44375,18 @@
         <v>2.926814614</v>
       </c>
       <c r="DL101" t="n">
+        <v>12.682815205</v>
+      </c>
+      <c r="DM101" t="n">
         <v>927</v>
       </c>
-      <c r="DM101" t="inlineStr">
+      <c r="DN101" t="inlineStr">
         <is>
           <t>3^2 × 103</t>
         </is>
+      </c>
+      <c r="DO101" t="n">
+        <v>322163.74</v>
       </c>
     </row>
   </sheetData>
